--- a/SageReasoning_BreakEven_Analysis.xlsx
+++ b/SageReasoning_BreakEven_Analysis.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">API markup (revenue per call / cost per call)</t>
   </si>
   <si>
-    <t xml:space="preserve">150% of Anthropic cost = 50% gross margin on API calls</t>
+    <t xml:space="preserve">200% of Anthropic cost = 100% gross margin on API calls</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue per API call</t>
@@ -1236,6 +1236,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>3</v>
@@ -1329,6 +1330,7 @@
         <v>5674</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>19</v>
@@ -1433,6 +1435,7 @@
         <v>279</v>
       </c>
     </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>37</v>
@@ -1456,7 +1459,7 @@
         <v>40</v>
       </c>
       <c r="B26" s="11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>41</v>
@@ -1468,7 +1471,7 @@
       </c>
       <c r="B27" s="12" t="n">
         <f aca="false">B25*B26</f>
-        <v>0.0225</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1477,7 +1480,7 @@
       </c>
       <c r="B28" s="12" t="n">
         <f aca="false">B27-B25</f>
-        <v>0.0075</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1491,6 +1494,7 @@
         <v>46</v>
       </c>
     </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>47</v>
@@ -1623,6 +1627,7 @@
         <v>70</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>71</v>
@@ -1723,6 +1728,7 @@
         <v>340</v>
       </c>
     </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>74</v>
@@ -1900,6 +1906,7 @@
         <v>40</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>78</v>
@@ -1981,47 +1988,47 @@
       </c>
       <c r="C14" s="18" t="n">
         <f aca="false">C9*Assumptions!B35*Assumptions!B27</f>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">D9*Assumptions!B35*Assumptions!B27</f>
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">E9*Assumptions!B35*Assumptions!B27</f>
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">F9*Assumptions!B35*Assumptions!B27</f>
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">G9*Assumptions!B35*Assumptions!B27</f>
-        <v>315</v>
+        <v>420</v>
       </c>
       <c r="H14" s="18" t="n">
         <f aca="false">H9*Assumptions!B35*Assumptions!B27</f>
-        <v>405</v>
+        <v>540</v>
       </c>
       <c r="I14" s="18" t="n">
         <f aca="false">I9*Assumptions!B35*Assumptions!B27</f>
-        <v>540</v>
+        <v>720</v>
       </c>
       <c r="J14" s="18" t="n">
         <f aca="false">J9*Assumptions!B35*Assumptions!B27</f>
-        <v>675</v>
+        <v>900</v>
       </c>
       <c r="K14" s="18" t="n">
         <f aca="false">K9*Assumptions!B35*Assumptions!B27</f>
-        <v>855</v>
+        <v>1140</v>
       </c>
       <c r="L14" s="18" t="n">
         <f aca="false">L9*Assumptions!B35*Assumptions!B27</f>
-        <v>1035</v>
+        <v>1380</v>
       </c>
       <c r="M14" s="18" t="n">
         <f aca="false">M9*Assumptions!B35*Assumptions!B27</f>
-        <v>1215</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2169,53 +2176,54 @@
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">SUM(C13:C17)</f>
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">SUM(D13:D17)</f>
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="E18" s="19" t="n">
         <f aca="false">SUM(E13:E17)</f>
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="F18" s="19" t="n">
         <f aca="false">SUM(F13:F17)</f>
-        <v>411</v>
+        <v>486</v>
       </c>
       <c r="G18" s="19" t="n">
         <f aca="false">SUM(G13:G17)</f>
-        <v>583</v>
+        <v>688</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">SUM(H13:H17)</f>
-        <v>750</v>
+        <v>885</v>
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">SUM(I13:I17)</f>
-        <v>986</v>
+        <v>1166</v>
       </c>
       <c r="J18" s="19" t="n">
         <f aca="false">SUM(J13:J17)</f>
-        <v>1717</v>
+        <v>1942</v>
       </c>
       <c r="K18" s="19" t="n">
         <f aca="false">SUM(K13:K17)</f>
-        <v>2000</v>
+        <v>2285</v>
       </c>
       <c r="L18" s="19" t="n">
         <f aca="false">SUM(L13:L17)</f>
-        <v>2285</v>
+        <v>2630</v>
       </c>
       <c r="M18" s="19" t="n">
         <f aca="false">SUM(M13:M17)</f>
-        <v>2585</v>
+        <v>2990</v>
       </c>
       <c r="N18" s="9" t="n">
         <f aca="false">SUM(B18:M18)</f>
-        <v>11808</v>
-      </c>
-    </row>
+        <v>13653</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>85</v>
@@ -2391,47 +2399,47 @@
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">C18*0.02</f>
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">D18*0.02</f>
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="E24" s="18" t="n">
         <f aca="false">E18*0.02</f>
-        <v>5.36</v>
+        <v>6.26</v>
       </c>
       <c r="F24" s="18" t="n">
         <f aca="false">F18*0.02</f>
-        <v>8.22</v>
+        <v>9.72</v>
       </c>
       <c r="G24" s="18" t="n">
         <f aca="false">G18*0.02</f>
-        <v>11.66</v>
+        <v>13.76</v>
       </c>
       <c r="H24" s="18" t="n">
         <f aca="false">H18*0.02</f>
-        <v>15</v>
+        <v>17.7</v>
       </c>
       <c r="I24" s="18" t="n">
         <f aca="false">I18*0.02</f>
-        <v>19.72</v>
+        <v>23.32</v>
       </c>
       <c r="J24" s="18" t="n">
         <f aca="false">J18*0.02</f>
-        <v>34.34</v>
+        <v>38.84</v>
       </c>
       <c r="K24" s="18" t="n">
         <f aca="false">K18*0.02</f>
-        <v>40</v>
+        <v>45.7</v>
       </c>
       <c r="L24" s="18" t="n">
         <f aca="false">L18*0.02</f>
-        <v>45.7</v>
+        <v>52.6</v>
       </c>
       <c r="M24" s="18" t="n">
         <f aca="false">M18*0.02</f>
-        <v>51.7</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2444,53 +2452,54 @@
       </c>
       <c r="C25" s="20" t="n">
         <f aca="false">SUM(C21:C24)</f>
-        <v>330.42</v>
+        <v>330.72</v>
       </c>
       <c r="D25" s="20" t="n">
         <f aca="false">SUM(D21:D24)</f>
-        <v>371.8</v>
+        <v>372.4</v>
       </c>
       <c r="E25" s="20" t="n">
         <f aca="false">SUM(E21:E24)</f>
-        <v>414.36</v>
+        <v>415.26</v>
       </c>
       <c r="F25" s="20" t="n">
         <f aca="false">SUM(F21:F24)</f>
-        <v>487.22</v>
+        <v>488.72</v>
       </c>
       <c r="G25" s="20" t="n">
         <f aca="false">SUM(G21:G24)</f>
-        <v>560.66</v>
+        <v>562.76</v>
       </c>
       <c r="H25" s="20" t="n">
         <f aca="false">SUM(H21:H24)</f>
-        <v>634</v>
+        <v>636.7</v>
       </c>
       <c r="I25" s="20" t="n">
         <f aca="false">SUM(I21:I24)</f>
-        <v>738.72</v>
+        <v>742.32</v>
       </c>
       <c r="J25" s="20" t="n">
         <f aca="false">SUM(J21:J24)</f>
-        <v>853.34</v>
+        <v>857.84</v>
       </c>
       <c r="K25" s="20" t="n">
         <f aca="false">SUM(K21:K24)</f>
-        <v>989</v>
+        <v>994.7</v>
       </c>
       <c r="L25" s="20" t="n">
         <f aca="false">SUM(L21:L24)</f>
-        <v>1124.7</v>
+        <v>1131.6</v>
       </c>
       <c r="M25" s="20" t="n">
         <f aca="false">SUM(M21:M24)</f>
-        <v>1260.7</v>
+        <v>1268.8</v>
       </c>
       <c r="N25" s="9" t="n">
         <f aca="false">SUM(B25:M25)</f>
-        <v>8059.16</v>
-      </c>
-    </row>
+        <v>8096.06</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>91</v>
@@ -2519,47 +2528,47 @@
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">C18-C25</f>
-        <v>-259.42</v>
+        <v>-244.72</v>
       </c>
       <c r="D28" s="21" t="n">
         <f aca="false">D18-D25</f>
-        <v>-231.8</v>
+        <v>-202.4</v>
       </c>
       <c r="E28" s="21" t="n">
         <f aca="false">E18-E25</f>
-        <v>-146.36</v>
+        <v>-102.26</v>
       </c>
       <c r="F28" s="21" t="n">
         <f aca="false">F18-F25</f>
-        <v>-76.22</v>
+        <v>-2.72000000000003</v>
       </c>
       <c r="G28" s="21" t="n">
         <f aca="false">G18-G25</f>
-        <v>22.34</v>
+        <v>125.24</v>
       </c>
       <c r="H28" s="21" t="n">
         <f aca="false">H18-H25</f>
-        <v>116</v>
+        <v>248.3</v>
       </c>
       <c r="I28" s="21" t="n">
         <f aca="false">I18-I25</f>
-        <v>247.28</v>
+        <v>423.68</v>
       </c>
       <c r="J28" s="21" t="n">
         <f aca="false">J18-J25</f>
-        <v>863.66</v>
+        <v>1084.16</v>
       </c>
       <c r="K28" s="21" t="n">
         <f aca="false">K18-K25</f>
-        <v>1011</v>
+        <v>1290.3</v>
       </c>
       <c r="L28" s="21" t="n">
         <f aca="false">L18-L25</f>
-        <v>1160.3</v>
+        <v>1498.4</v>
       </c>
       <c r="M28" s="21" t="n">
         <f aca="false">M18-M25</f>
-        <v>1324.3</v>
+        <v>1721.2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2572,49 +2581,50 @@
       </c>
       <c r="C29" s="21" t="n">
         <f aca="false">B29+C28</f>
-        <v>-6215.66</v>
+        <v>-6200.96</v>
       </c>
       <c r="D29" s="21" t="n">
         <f aca="false">C29+D28</f>
-        <v>-6447.46</v>
+        <v>-6403.36</v>
       </c>
       <c r="E29" s="21" t="n">
         <f aca="false">D29+E28</f>
-        <v>-6593.82</v>
+        <v>-6505.62</v>
       </c>
       <c r="F29" s="21" t="n">
         <f aca="false">E29+F28</f>
-        <v>-6670.04</v>
+        <v>-6508.34</v>
       </c>
       <c r="G29" s="21" t="n">
         <f aca="false">F29+G28</f>
-        <v>-6647.7</v>
+        <v>-6383.1</v>
       </c>
       <c r="H29" s="21" t="n">
         <f aca="false">G29+H28</f>
-        <v>-6531.7</v>
+        <v>-6134.8</v>
       </c>
       <c r="I29" s="21" t="n">
         <f aca="false">H29+I28</f>
-        <v>-6284.42</v>
+        <v>-5711.12</v>
       </c>
       <c r="J29" s="21" t="n">
         <f aca="false">I29+J28</f>
-        <v>-5420.76</v>
+        <v>-4626.96</v>
       </c>
       <c r="K29" s="21" t="n">
         <f aca="false">J29+K28</f>
-        <v>-4409.76</v>
+        <v>-3336.66</v>
       </c>
       <c r="L29" s="21" t="n">
         <f aca="false">K29+L28</f>
-        <v>-3249.46</v>
+        <v>-1838.26</v>
       </c>
       <c r="M29" s="21" t="n">
         <f aca="false">L29+M28</f>
-        <v>-1925.16</v>
-      </c>
-    </row>
+        <v>-117.06</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
         <v>94</v>
@@ -2625,47 +2635,47 @@
       </c>
       <c r="C31" s="23" t="n">
         <f aca="false">IF(C14=0,0,(C14-C22)/C14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D31" s="23" t="n">
         <f aca="false">IF(D14=0,0,(D14-D22)/D14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="23" t="n">
         <f aca="false">IF(E14=0,0,(E14-E22)/E14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="23" t="n">
         <f aca="false">IF(F14=0,0,(F14-F22)/F14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="23" t="n">
         <f aca="false">IF(G14=0,0,(G14-G22)/G14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="H31" s="23" t="n">
         <f aca="false">IF(H14=0,0,(H14-H22)/H14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">IF(I14=0,0,(I14-I22)/I14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="J31" s="23" t="n">
         <f aca="false">IF(J14=0,0,(J14-J22)/J14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="K31" s="23" t="n">
         <f aca="false">IF(K14=0,0,(K14-K22)/K14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="L31" s="23" t="n">
         <f aca="false">IF(L14=0,0,(L14-L22)/L14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="M31" s="23" t="n">
         <f aca="false">IF(M14=0,0,(M14-M22)/M14)</f>
-        <v>0.333333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2706,6 +2716,7 @@
         <v>98</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>99</v>
@@ -2788,6 +2799,7 @@
         <v>5000</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>106</v>
@@ -2854,15 +2866,15 @@
       </c>
       <c r="B14" s="18" t="n">
         <f aca="false">B12*B8*Assumptions!B27</f>
-        <v>33.75</v>
+        <v>45</v>
       </c>
       <c r="C14" s="18" t="n">
         <f aca="false">C12*C8*Assumptions!B27</f>
-        <v>1215</v>
+        <v>1620</v>
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">D12*D8*Assumptions!B27</f>
-        <v>13500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2885,17 +2897,18 @@
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">SUM(B13:B15)</f>
-        <v>209.75</v>
+        <v>221</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">SUM(C13:C15)</f>
-        <v>2055</v>
+        <v>2460</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">SUM(D13:D15)</f>
-        <v>16600</v>
-      </c>
-    </row>
+        <v>21100</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>112</v>
@@ -2956,6 +2969,7 @@
         <v>9379</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>116</v>
@@ -2971,15 +2985,15 @@
       </c>
       <c r="B24" s="21" t="n">
         <f aca="false">B16-B21</f>
-        <v>-191.75</v>
+        <v>-180.5</v>
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">C16-C21</f>
-        <v>866</v>
+        <v>1271</v>
       </c>
       <c r="D24" s="21" t="n">
         <f aca="false">D16-D21</f>
-        <v>7221</v>
+        <v>11721</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2988,15 +3002,15 @@
       </c>
       <c r="B25" s="9" t="n">
         <f aca="false">B16*12</f>
-        <v>2517</v>
+        <v>2652</v>
       </c>
       <c r="C25" s="9" t="n">
         <f aca="false">C16*12</f>
-        <v>24660</v>
+        <v>29520</v>
       </c>
       <c r="D25" s="9" t="n">
         <f aca="false">D16*12</f>
-        <v>199200</v>
+        <v>253200</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3011,6 +3025,7 @@
         <v>120</v>
       </c>
     </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>121</v>
@@ -3067,6 +3082,7 @@
         <v>125</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>126</v>
@@ -3113,6 +3129,7 @@
         <v>820</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>132</v>
@@ -3126,7 +3143,7 @@
       </c>
       <c r="B10" s="27" t="n">
         <f aca="false">5*Assumptions!B35*Assumptions!B28</f>
-        <v>75</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3135,7 +3152,7 @@
       </c>
       <c r="B11" s="27" t="n">
         <f aca="false">MAX(B4-B10,0)</f>
-        <v>204</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3144,9 +3161,10 @@
       </c>
       <c r="B12" s="31" t="n">
         <f aca="false">IF(B11=0,0,ROUNDUP(B11/B5,0))</f>
-        <v>30</v>
-      </c>
-    </row>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>136</v>
@@ -3160,7 +3178,7 @@
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">Assumptions!B28</f>
-        <v>0.0075</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3169,7 +3187,7 @@
       </c>
       <c r="B16" s="33" t="n">
         <f aca="false">ROUNDUP(B4/B15,0)</f>
-        <v>37200</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3178,9 +3196,10 @@
       </c>
       <c r="B17" s="30" t="n">
         <f aca="false">ROUNDUP(B16/Assumptions!B35,0)</f>
-        <v>19</v>
-      </c>
-    </row>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>139</v>
@@ -3203,7 +3222,7 @@
       </c>
       <c r="B21" s="27" t="n">
         <f aca="false">AVERAGE('12-Month Projection'!H28:M28)</f>
-        <v>787.09</v>
+        <v>1044.34</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3212,7 +3231,7 @@
       </c>
       <c r="B22" s="30" t="n">
         <f aca="false">IF(B21&gt;0,ROUNDUP(B20/B21,1),"N/A")</f>
-        <v>7.3</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -3256,6 +3275,7 @@
         <v>147</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>148</v>
@@ -3363,6 +3383,7 @@
         <v>168</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>169</v>
@@ -3470,6 +3491,7 @@
         <v>187</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>188</v>
